--- a/HTDW_4438/urdf/initial_joint_properties.xlsx
+++ b/HTDW_4438/urdf/initial_joint_properties.xlsx
@@ -447,9 +447,9 @@
     <col width="15.6" customWidth="1" min="5" max="5"/>
     <col width="14.4" customWidth="1" min="6" max="6"/>
     <col width="14.4" customWidth="1" min="7" max="7"/>
-    <col width="14.4" customWidth="1" min="8" max="8"/>
+    <col width="15.6" customWidth="1" min="8" max="8"/>
     <col width="14.4" customWidth="1" min="9" max="9"/>
-    <col width="14.4" customWidth="1" min="10" max="10"/>
+    <col width="15.6" customWidth="1" min="10" max="10"/>
     <col width="14.4" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -591,34 +591,34 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.47279447</v>
+        <v>0.48086181</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-0.00297476</v>
+        <v>-0.00360471</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.01800033</v>
+        <v>-0.01763227</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.02107619</v>
+        <v>-0.02190343</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.00103183</v>
+        <v>0.00103502</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.421e-05</v>
+        <v>2.935e-05</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-7.152000000000001e-05</v>
+        <v>-8.603e-05</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.00094144</v>
+        <v>0.00094426</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.00018112</v>
+        <v>0.00018729</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.00024056</v>
+        <v>0.00024889</v>
       </c>
     </row>
     <row r="5">
@@ -739,34 +739,34 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.47279491</v>
+        <v>0.48086142</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-0.00313741</v>
+        <v>-0.00559051</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.01800027</v>
+        <v>0.01763224</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.02121661</v>
+        <v>-0.02107369</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.0010289</v>
+        <v>0.00101933</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-2.518e-05</v>
+        <v>-4.59e-05</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-6.847e-05</v>
+        <v>-0.00016158</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.00093817</v>
+        <v>0.0009526200000000001</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0.0001799</v>
+        <v>-0.00017843</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.00024021</v>
+        <v>0.00027294</v>
       </c>
     </row>
     <row r="9">
@@ -887,34 +887,34 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.47279447</v>
+        <v>0.48086181</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.0032586</v>
+        <v>-0.00555466</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-0.01800033</v>
+        <v>-0.01763227</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.02118103</v>
+        <v>-0.02101551</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.00102822</v>
+        <v>0.00102307</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2.639e-05</v>
+        <v>4.602e-05</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-6.677e-05</v>
+        <v>-0.00015399</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.00093851</v>
+        <v>0.00095399</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.00018193</v>
+        <v>0.00018026</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.00024123</v>
+        <v>0.00027057</v>
       </c>
     </row>
     <row r="13">
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.47279491</v>
+        <v>0.48086142</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.00313741</v>
+        <v>-0.00521957</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.01800027</v>
+        <v>0.01761785</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.02121661</v>
+        <v>-0.02116423</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.0010289</v>
+        <v>0.00102378</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.518e-05</v>
+        <v>-4.288e-05</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-6.847e-05</v>
+        <v>-0.00015179</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.00093817</v>
+        <v>0.00095271</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.0001799</v>
+        <v>-0.00018005</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.00024021</v>
+        <v>0.00026924</v>
       </c>
     </row>
     <row r="17">
